--- a/research/traditional_assets/database/data/serbia/serbia_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/serbia/serbia_insurance_general.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.06849999999999999</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E2">
-        <v>0.165</v>
+        <v>0.506</v>
       </c>
       <c r="G2">
-        <v>0.1419354838709677</v>
+        <v>0.1153971886237332</v>
       </c>
       <c r="H2">
-        <v>0.1419354838709677</v>
+        <v>0.1153971886237332</v>
       </c>
       <c r="I2">
-        <v>0.1207373271889401</v>
+        <v>0.05622752533507682</v>
       </c>
       <c r="J2">
-        <v>0.1067132222616093</v>
+        <v>0.0457203615098352</v>
       </c>
       <c r="K2">
-        <v>33.9</v>
+        <v>15.6</v>
       </c>
       <c r="L2">
-        <v>0.104147465437788</v>
+        <v>0.05099705786204643</v>
       </c>
       <c r="M2">
-        <v>5.12</v>
+        <v>13.1</v>
       </c>
       <c r="N2">
-        <v>0.01858439201451906</v>
+        <v>0.08875338753387534</v>
       </c>
       <c r="O2">
-        <v>0.1510324483775811</v>
+        <v>0.8397435897435898</v>
       </c>
       <c r="P2">
-        <v>5.12</v>
+        <v>13.1</v>
       </c>
       <c r="Q2">
-        <v>0.01858439201451906</v>
+        <v>0.08875338753387534</v>
       </c>
       <c r="R2">
-        <v>0.1510324483775811</v>
+        <v>0.8397435897435898</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>37.6</v>
+        <v>19.3</v>
       </c>
       <c r="V2">
-        <v>0.1364791288566243</v>
+        <v>0.1307588075880759</v>
       </c>
       <c r="W2">
-        <v>0.2417974322396576</v>
+        <v>0.1007101355713363</v>
       </c>
       <c r="X2">
-        <v>0.06546765024955785</v>
+        <v>0.1096912755044149</v>
       </c>
       <c r="Y2">
-        <v>0.1763297819900998</v>
+        <v>-0.008981139933078516</v>
       </c>
       <c r="Z2">
-        <v>3.083554376657825</v>
+        <v>2.562405763109398</v>
       </c>
       <c r="AA2">
-        <v>0.3290560235520447</v>
+        <v>0.1171541178242468</v>
       </c>
       <c r="AB2">
-        <v>0.06533740642977109</v>
+        <v>0.1081705818676561</v>
       </c>
       <c r="AC2">
-        <v>0.2637186171222736</v>
+        <v>0.008983535956590724</v>
       </c>
       <c r="AD2">
-        <v>2.08</v>
+        <v>7.45</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>2.08</v>
+        <v>7.45</v>
       </c>
       <c r="AG2">
-        <v>-35.52</v>
+        <v>-11.85</v>
       </c>
       <c r="AH2">
-        <v>0.007493335254701348</v>
+        <v>0.04804901644630765</v>
       </c>
       <c r="AI2">
-        <v>0.01298539143463603</v>
+        <v>0.04285303422490653</v>
       </c>
       <c r="AJ2">
-        <v>-0.1480123343611968</v>
+        <v>-0.08729281767955802</v>
       </c>
       <c r="AK2">
-        <v>-0.2897699461576114</v>
+        <v>-0.07667421546425106</v>
       </c>
       <c r="AL2">
-        <v>0.335</v>
+        <v>0.751</v>
       </c>
       <c r="AM2">
-        <v>0.335</v>
+        <v>0.751</v>
       </c>
       <c r="AN2">
-        <v>0.04814814814814815</v>
+        <v>0.3156779661016949</v>
       </c>
       <c r="AO2">
-        <v>117.3134328358209</v>
+        <v>22.90279627163781</v>
       </c>
       <c r="AP2">
-        <v>-0.8222222222222222</v>
+        <v>-0.5021186440677966</v>
       </c>
       <c r="AQ2">
-        <v>117.3134328358209</v>
+        <v>22.90279627163781</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.06849999999999999</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E3">
-        <v>0.165</v>
+        <v>0.506</v>
       </c>
       <c r="G3">
-        <v>0.1419354838709677</v>
+        <v>0.1153971886237332</v>
       </c>
       <c r="H3">
-        <v>0.1419354838709677</v>
+        <v>0.1153971886237332</v>
       </c>
       <c r="I3">
-        <v>0.1207373271889401</v>
+        <v>0.05622752533507682</v>
       </c>
       <c r="J3">
-        <v>0.1067132222616093</v>
+        <v>0.0457203615098352</v>
       </c>
       <c r="K3">
-        <v>33.9</v>
+        <v>15.6</v>
       </c>
       <c r="L3">
-        <v>0.104147465437788</v>
+        <v>0.05099705786204643</v>
       </c>
       <c r="M3">
-        <v>5.12</v>
+        <v>13.1</v>
       </c>
       <c r="N3">
-        <v>0.01858439201451906</v>
+        <v>0.08875338753387534</v>
       </c>
       <c r="O3">
-        <v>0.1510324483775811</v>
+        <v>0.8397435897435898</v>
       </c>
       <c r="P3">
-        <v>5.12</v>
+        <v>13.1</v>
       </c>
       <c r="Q3">
-        <v>0.01858439201451906</v>
+        <v>0.08875338753387534</v>
       </c>
       <c r="R3">
-        <v>0.1510324483775811</v>
+        <v>0.8397435897435898</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>37.6</v>
+        <v>19.3</v>
       </c>
       <c r="V3">
-        <v>0.1364791288566243</v>
+        <v>0.1307588075880759</v>
       </c>
       <c r="W3">
-        <v>0.2417974322396576</v>
+        <v>0.1007101355713363</v>
       </c>
       <c r="X3">
-        <v>0.06546765024955785</v>
+        <v>0.1096912755044149</v>
       </c>
       <c r="Y3">
-        <v>0.1763297819900998</v>
+        <v>-0.008981139933078516</v>
       </c>
       <c r="Z3">
-        <v>3.083554376657825</v>
+        <v>2.562405763109398</v>
       </c>
       <c r="AA3">
-        <v>0.3290560235520447</v>
+        <v>0.1171541178242468</v>
       </c>
       <c r="AB3">
-        <v>0.06533740642977109</v>
+        <v>0.1081705818676561</v>
       </c>
       <c r="AC3">
-        <v>0.2637186171222736</v>
+        <v>0.008983535956590724</v>
       </c>
       <c r="AD3">
-        <v>2.08</v>
+        <v>7.45</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>2.08</v>
+        <v>7.45</v>
       </c>
       <c r="AG3">
-        <v>-35.52</v>
+        <v>-11.85</v>
       </c>
       <c r="AH3">
-        <v>0.007493335254701348</v>
+        <v>0.04804901644630765</v>
       </c>
       <c r="AI3">
-        <v>0.01298539143463603</v>
+        <v>0.04285303422490653</v>
       </c>
       <c r="AJ3">
-        <v>-0.1480123343611968</v>
+        <v>-0.08729281767955802</v>
       </c>
       <c r="AK3">
-        <v>-0.2897699461576114</v>
+        <v>-0.07667421546425106</v>
       </c>
       <c r="AL3">
-        <v>0.335</v>
+        <v>0.751</v>
       </c>
       <c r="AM3">
-        <v>0.335</v>
+        <v>0.751</v>
       </c>
       <c r="AN3">
-        <v>0.04814814814814815</v>
+        <v>0.3156779661016949</v>
       </c>
       <c r="AO3">
-        <v>117.3134328358209</v>
+        <v>22.90279627163781</v>
       </c>
       <c r="AP3">
-        <v>-0.8222222222222222</v>
+        <v>-0.5021186440677966</v>
       </c>
       <c r="AQ3">
-        <v>117.3134328358209</v>
+        <v>22.90279627163781</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/serbia/serbia_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/serbia/serbia_insurance_general.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.07000000000000001</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="E2">
-        <v>0.506</v>
+        <v>-0.0152</v>
       </c>
       <c r="G2">
-        <v>0.1153971886237332</v>
+        <v>0.04816577989358722</v>
       </c>
       <c r="H2">
-        <v>0.1153971886237332</v>
+        <v>0.04816577989358722</v>
       </c>
       <c r="I2">
-        <v>0.05622752533507682</v>
+        <v>0.02856342761131335</v>
       </c>
       <c r="J2">
-        <v>0.0457203615098352</v>
+        <v>0.02671604174590502</v>
       </c>
       <c r="K2">
-        <v>15.6</v>
+        <v>18.2</v>
       </c>
       <c r="L2">
-        <v>0.05099705786204643</v>
+        <v>0.05096611593391207</v>
       </c>
       <c r="M2">
-        <v>13.1</v>
+        <v>15.4</v>
       </c>
       <c r="N2">
-        <v>0.08875338753387534</v>
+        <v>0.113905325443787</v>
       </c>
       <c r="O2">
-        <v>0.8397435897435898</v>
+        <v>0.8461538461538463</v>
       </c>
       <c r="P2">
-        <v>13.1</v>
+        <v>15.4</v>
       </c>
       <c r="Q2">
-        <v>0.08875338753387534</v>
+        <v>0.113905325443787</v>
       </c>
       <c r="R2">
-        <v>0.8397435897435898</v>
+        <v>0.8461538461538463</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>19.3</v>
+        <v>35.1</v>
       </c>
       <c r="V2">
-        <v>0.1307588075880759</v>
+        <v>0.2596153846153846</v>
       </c>
       <c r="W2">
-        <v>0.1007101355713363</v>
+        <v>0.1116564417177914</v>
       </c>
       <c r="X2">
-        <v>0.1096912755044149</v>
+        <v>0.09936921811914376</v>
       </c>
       <c r="Y2">
-        <v>-0.008981139933078516</v>
+        <v>0.01228722359864765</v>
       </c>
       <c r="Z2">
-        <v>2.562405763109398</v>
+        <v>2.362553754548463</v>
       </c>
       <c r="AA2">
-        <v>0.1171541178242468</v>
+        <v>0.06311808473346138</v>
       </c>
       <c r="AB2">
-        <v>0.1081705818676561</v>
+        <v>0.09690594114736462</v>
       </c>
       <c r="AC2">
-        <v>0.008983535956590724</v>
+        <v>-0.03378785641390324</v>
       </c>
       <c r="AD2">
-        <v>7.45</v>
+        <v>12.9</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>7.45</v>
+        <v>12.9</v>
       </c>
       <c r="AG2">
-        <v>-11.85</v>
+        <v>-22.2</v>
       </c>
       <c r="AH2">
-        <v>0.04804901644630765</v>
+        <v>0.08710330857528698</v>
       </c>
       <c r="AI2">
-        <v>0.04285303422490653</v>
+        <v>0.06571574121242996</v>
       </c>
       <c r="AJ2">
-        <v>-0.08729281767955802</v>
+        <v>-0.1964601769911505</v>
       </c>
       <c r="AK2">
-        <v>-0.07667421546425106</v>
+        <v>-0.1377171215880894</v>
       </c>
       <c r="AL2">
-        <v>0.751</v>
+        <v>0.576</v>
       </c>
       <c r="AM2">
-        <v>0.751</v>
+        <v>0.576</v>
       </c>
       <c r="AN2">
-        <v>0.3156779661016949</v>
+        <v>0.7247191011235955</v>
       </c>
       <c r="AO2">
-        <v>22.90279627163781</v>
+        <v>17.70833333333333</v>
       </c>
       <c r="AP2">
-        <v>-0.5021186440677966</v>
+        <v>-1.247191011235955</v>
       </c>
       <c r="AQ2">
-        <v>22.90279627163781</v>
+        <v>17.70833333333333</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.07000000000000001</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="E3">
-        <v>0.506</v>
+        <v>-0.0152</v>
       </c>
       <c r="G3">
-        <v>0.1153971886237332</v>
+        <v>0.04816577989358722</v>
       </c>
       <c r="H3">
-        <v>0.1153971886237332</v>
+        <v>0.04816577989358722</v>
       </c>
       <c r="I3">
-        <v>0.05622752533507682</v>
+        <v>0.02856342761131335</v>
       </c>
       <c r="J3">
-        <v>0.0457203615098352</v>
+        <v>0.02671604174590502</v>
       </c>
       <c r="K3">
-        <v>15.6</v>
+        <v>18.2</v>
       </c>
       <c r="L3">
-        <v>0.05099705786204643</v>
+        <v>0.05096611593391207</v>
       </c>
       <c r="M3">
-        <v>13.1</v>
+        <v>15.4</v>
       </c>
       <c r="N3">
-        <v>0.08875338753387534</v>
+        <v>0.113905325443787</v>
       </c>
       <c r="O3">
-        <v>0.8397435897435898</v>
+        <v>0.8461538461538463</v>
       </c>
       <c r="P3">
-        <v>13.1</v>
+        <v>15.4</v>
       </c>
       <c r="Q3">
-        <v>0.08875338753387534</v>
+        <v>0.113905325443787</v>
       </c>
       <c r="R3">
-        <v>0.8397435897435898</v>
+        <v>0.8461538461538463</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>19.3</v>
+        <v>35.1</v>
       </c>
       <c r="V3">
-        <v>0.1307588075880759</v>
+        <v>0.2596153846153846</v>
       </c>
       <c r="W3">
-        <v>0.1007101355713363</v>
+        <v>0.1116564417177914</v>
       </c>
       <c r="X3">
-        <v>0.1096912755044149</v>
+        <v>0.09936921811914376</v>
       </c>
       <c r="Y3">
-        <v>-0.008981139933078516</v>
+        <v>0.01228722359864765</v>
       </c>
       <c r="Z3">
-        <v>2.562405763109398</v>
+        <v>2.362553754548463</v>
       </c>
       <c r="AA3">
-        <v>0.1171541178242468</v>
+        <v>0.06311808473346138</v>
       </c>
       <c r="AB3">
-        <v>0.1081705818676561</v>
+        <v>0.09690594114736462</v>
       </c>
       <c r="AC3">
-        <v>0.008983535956590724</v>
+        <v>-0.03378785641390324</v>
       </c>
       <c r="AD3">
-        <v>7.45</v>
+        <v>12.9</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>7.45</v>
+        <v>12.9</v>
       </c>
       <c r="AG3">
-        <v>-11.85</v>
+        <v>-22.2</v>
       </c>
       <c r="AH3">
-        <v>0.04804901644630765</v>
+        <v>0.08710330857528698</v>
       </c>
       <c r="AI3">
-        <v>0.04285303422490653</v>
+        <v>0.06571574121242996</v>
       </c>
       <c r="AJ3">
-        <v>-0.08729281767955802</v>
+        <v>-0.1964601769911505</v>
       </c>
       <c r="AK3">
-        <v>-0.07667421546425106</v>
+        <v>-0.1377171215880894</v>
       </c>
       <c r="AL3">
-        <v>0.751</v>
+        <v>0.576</v>
       </c>
       <c r="AM3">
-        <v>0.751</v>
+        <v>0.576</v>
       </c>
       <c r="AN3">
-        <v>0.3156779661016949</v>
+        <v>0.7247191011235955</v>
       </c>
       <c r="AO3">
-        <v>22.90279627163781</v>
+        <v>17.70833333333333</v>
       </c>
       <c r="AP3">
-        <v>-0.5021186440677966</v>
+        <v>-1.247191011235955</v>
       </c>
       <c r="AQ3">
-        <v>22.90279627163781</v>
+        <v>17.70833333333333</v>
       </c>
     </row>
   </sheetData>
